--- a/artfynd/A 47216-2025 artfynd.xlsx
+++ b/artfynd/A 47216-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1918668</v>
+        <v>85198</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559919.1394552605</v>
+        <v>559942</v>
       </c>
       <c r="R2" t="n">
-        <v>7031819.470289195</v>
+        <v>7031914</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,9 @@
           <t>2008-07-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>friskfuktig mark, blåbärstyp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>i kanten mellan contortaungskog och äldre granskog</t>
+          <t>i kanten mellan sumpskog och contortaungskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>på bark på stam av levande sälg (50 cm dbh)</t>
+          <t>riklig på kvistar av torrgran (24 cm dbh, ca 120 år)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>827273</v>
+        <v>85199</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559919.1394552605</v>
+        <v>559949</v>
       </c>
       <c r="R3" t="n">
-        <v>7031819.470289195</v>
+        <v>7031869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,24 +854,9 @@
           <t>2008-07-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>friskfuktig mark, blåbärstyp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +870,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>i kanten mellan contortaungskog och äldre granskog</t>
+          <t>i 120-årig granskog av frisk blåbärstyp</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>på bark på stam av levande sälg (50 cm dbh)</t>
+          <t>på död kvist av levande gran (28 cm dbh, ca 110 år</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -930,6 +890,238 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Vindkraft 2008 Björkhöjden</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>827273</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nordost om Helgamässtjärnen, 3 km S. Hocksjön, 20 km SV Ramsele k:a, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>559919</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7031819</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-07-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-07-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>friskfuktig mark, blåbärstyp</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>i kanten mellan contortaungskog och äldre granskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>på bark på stam av levande sälg (50 cm dbh)</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Vindkraft 2008 Björkhöjden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1918668</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordost om Helgamässtjärnen, 3 km S. Hocksjön, 20 km SV Ramsele k:a, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559919</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7031819</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2008-07-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2008-07-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>friskfuktig mark, blåbärstyp</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>i kanten mellan contortaungskog och äldre granskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>på bark på stam av levande sälg (50 cm dbh)</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Vindkraft 2008 Björkhöjden</t>
         </is>

--- a/artfynd/A 47216-2025 artfynd.xlsx
+++ b/artfynd/A 47216-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Vindkraft 2008 Björkhöjden</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85198</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Vindkraft 2008 Björkhöjden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85199</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Vindkraft 2008 Björkhöjden</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/827273</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,8 +1146,19 @@
           <t>Vindkraft 2008 Björkhöjden</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1918668</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>